--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_depmenores_a_2018_atacama.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_depmenores_a_2018_atacama.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 13:45</t>
+    <t xml:space="preserve">2026-09-24 00:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -546,10 +546,10 @@
         <v>9</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>-0.43</v>
@@ -572,7 +572,7 @@
         <v>-0.11</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>-0.24</v>
@@ -592,10 +592,10 @@
         <v>9</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>-0.35</v>
@@ -618,7 +618,7 @@
         <v>-0.05</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>-0.07</v>
@@ -641,7 +641,7 @@
         <v>-0.04</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>0.55</v>
@@ -661,13 +661,13 @@
         <v>9</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>-0.5</v>
+        <v>-0.47</v>
       </c>
     </row>
     <row r="8">
@@ -684,13 +684,13 @@
         <v>9</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.07</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="9">
@@ -707,13 +707,13 @@
         <v>9</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="10">
@@ -733,10 +733,10 @@
         <v>0.15</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-0.24</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="11">
@@ -753,13 +753,13 @@
         <v>9</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>-0.24</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="12">
@@ -776,13 +776,13 @@
         <v>9</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="13">
@@ -799,13 +799,13 @@
         <v>9</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>-0.1</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="14">
@@ -822,10 +822,10 @@
         <v>9</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.19</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>-0.17</v>
@@ -848,7 +848,7 @@
         <v>-0.06</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>0.19</v>
@@ -871,7 +871,7 @@
         <v>-0.38</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>-0.34</v>
@@ -891,13 +891,13 @@
         <v>9</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>-0.28</v>
+        <v>-0.27</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>-0.5</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="18">
@@ -917,7 +917,7 @@
         <v>-0.22</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>0.04</v>
